--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>46.23655913978497</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>46.39303482587065</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>27.23214285714284</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>26.99386503067485</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>29.30780559646537</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>30.90062111801242</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>14.65753424657534</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>25.78616352201257</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>28.64768683274022</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>9.0032154340836</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>32.35294117647061</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>17.68953068592056</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>17.78584392014519</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>32.87356321839081</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>26.71081677704194</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>4.059040590405893</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>17.93103448275863</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>16.43518518518519</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>13.07506053268765</v>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>27.01149425287357</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -844,9 +779,6 @@
       </c>
       <c r="E22">
         <v>31.83183183183182</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -632,152 +632,171 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B15">
-        <v>5.78</v>
+        <v>6.26</v>
       </c>
       <c r="C15">
-        <v>4.35</v>
+        <v>5.15</v>
       </c>
       <c r="D15">
-        <v>1.430000000000001</v>
+        <v>1.109999999999999</v>
       </c>
       <c r="E15">
-        <v>32.87356321839081</v>
+        <v>21.55339805825241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="B16">
-        <v>5.74</v>
+        <v>5.78</v>
       </c>
       <c r="C16">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="D16">
-        <v>1.21</v>
+        <v>1.430000000000001</v>
       </c>
       <c r="E16">
-        <v>26.71081677704194</v>
+        <v>32.87356321839081</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="B17">
-        <v>5.64</v>
+        <v>5.74</v>
       </c>
       <c r="C17">
-        <v>5.42</v>
+        <v>4.53</v>
       </c>
       <c r="D17">
-        <v>0.2199999999999998</v>
+        <v>1.21</v>
       </c>
       <c r="E17">
-        <v>4.059040590405893</v>
+        <v>26.71081677704194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="B18">
-        <v>5.13</v>
+        <v>5.64</v>
       </c>
       <c r="C18">
-        <v>4.35</v>
+        <v>5.42</v>
       </c>
       <c r="D18">
-        <v>0.7800000000000002</v>
+        <v>0.2199999999999998</v>
       </c>
       <c r="E18">
-        <v>17.93103448275863</v>
+        <v>4.059040590405893</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="B19">
-        <v>5.03</v>
+        <v>5.13</v>
       </c>
       <c r="C19">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="D19">
-        <v>0.71</v>
+        <v>0.7800000000000002</v>
       </c>
       <c r="E19">
-        <v>16.43518518518519</v>
+        <v>17.93103448275863</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="B20">
-        <v>4.67</v>
+        <v>5.03</v>
       </c>
       <c r="C20">
-        <v>4.13</v>
+        <v>4.32</v>
       </c>
       <c r="D20">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="E20">
-        <v>13.07506053268765</v>
+        <v>16.43518518518519</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B21">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="C21">
-        <v>3.48</v>
+        <v>4.13</v>
       </c>
       <c r="D21">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="E21">
-        <v>27.01149425287357</v>
+        <v>13.07506053268765</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>4.42</v>
+      </c>
+      <c r="C22">
+        <v>3.48</v>
+      </c>
+      <c r="D22">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E22">
+        <v>27.01149425287357</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Treguaco</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>4.39</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>3.33</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>1.06</v>
       </c>
-      <c r="E22">
+      <c r="E23">
         <v>31.83183183183182</v>
       </c>
     </row>
@@ -946,7 +965,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B16">

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_nuble.xlsx
@@ -807,7 +807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -816,11 +816,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -828,9 +823,6 @@
           <t>Bulnes</t>
         </is>
       </c>
-      <c r="B2">
-        <v>8.43</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -838,9 +830,6 @@
           <t>Chillán Viejo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>5.03</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,188 +837,131 @@
           <t>Chillán</t>
         </is>
       </c>
-      <c r="B4">
-        <v>5.13</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>11.77</v>
+          <t>Yungay</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5.74</v>
+          <t>Quillón</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coihueco</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>8.369999999999999</v>
+          <t>San Carlos</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>11.4</v>
+          <t>Treguaco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ninhue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>6.75</v>
+          <t>Ranquil</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>5.64</v>
+          <t>Portezuelo</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pemuco</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>7.23</v>
+          <t>Cobquecura</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pinto</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>8</v>
+          <t>Quirihue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>12.24</v>
+          <t>Coelemu</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quillón</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>8.779999999999999</v>
+          <t>Ninhue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>5.78</v>
+          <t>Pinto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ranquil</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>4.67</v>
+          <t>San Ignacio</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>6.49</v>
+          <t>Pemuco</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Fabián</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>6.78</v>
+          <t>San Nicolás</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>10.35</v>
+          <t>San Fabián</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>6.52</v>
+          <t>Ñiquén</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Treguaco</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>4.39</v>
+          <t>El Carmen</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>4.42</v>
+          <t>Coihueco</t>
+        </is>
       </c>
     </row>
   </sheetData>
